--- a/Traditional_Test_Cases/Traditional Test Cases.xlsx
+++ b/Traditional_Test_Cases/Traditional Test Cases.xlsx
@@ -1326,7 +1326,7 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3">
+    <row r="3" ht="112.5" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
@@ -1372,7 +1372,7 @@
       <c r="Y3" s="10"/>
       <c r="Z3" s="10"/>
     </row>
-    <row r="4">
+    <row r="4" ht="112.5" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -1418,7 +1418,7 @@
       <c r="Y4" s="10"/>
       <c r="Z4" s="10"/>
     </row>
-    <row r="5">
+    <row r="5" ht="112.5" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>28</v>
       </c>
@@ -1464,7 +1464,7 @@
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
     </row>
-    <row r="6">
+    <row r="6" ht="112.5" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>36</v>
       </c>
@@ -1510,7 +1510,7 @@
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
     </row>
-    <row r="7">
+    <row r="7" ht="112.5" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>43</v>
       </c>
@@ -1556,7 +1556,7 @@
       <c r="Y7" s="10"/>
       <c r="Z7" s="10"/>
     </row>
-    <row r="8">
+    <row r="8" ht="112.5" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="Y8" s="10"/>
       <c r="Z8" s="10"/>
     </row>
-    <row r="9">
+    <row r="9" ht="112.5" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>56</v>
       </c>
@@ -1648,7 +1648,7 @@
       <c r="Y9" s="10"/>
       <c r="Z9" s="10"/>
     </row>
-    <row r="10">
+    <row r="10" ht="112.5" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>62</v>
       </c>
@@ -1694,7 +1694,7 @@
       <c r="Y10" s="10"/>
       <c r="Z10" s="10"/>
     </row>
-    <row r="11">
+    <row r="11" ht="112.5" customHeight="1">
       <c r="A11" s="6" t="s">
         <v>68</v>
       </c>
@@ -1740,7 +1740,7 @@
       <c r="Y11" s="10"/>
       <c r="Z11" s="10"/>
     </row>
-    <row r="12">
+    <row r="12" ht="112.5" customHeight="1">
       <c r="A12" s="6" t="s">
         <v>75</v>
       </c>
@@ -1786,7 +1786,7 @@
       <c r="Y12" s="10"/>
       <c r="Z12" s="10"/>
     </row>
-    <row r="13">
+    <row r="13" ht="112.5" customHeight="1">
       <c r="A13" s="6" t="s">
         <v>81</v>
       </c>
@@ -1832,7 +1832,7 @@
       <c r="Y13" s="10"/>
       <c r="Z13" s="10"/>
     </row>
-    <row r="14">
+    <row r="14" ht="112.5" customHeight="1">
       <c r="A14" s="6" t="s">
         <v>86</v>
       </c>
@@ -1878,7 +1878,7 @@
       <c r="Y14" s="10"/>
       <c r="Z14" s="10"/>
     </row>
-    <row r="15">
+    <row r="15" ht="112.5" customHeight="1">
       <c r="A15" s="6" t="s">
         <v>92</v>
       </c>
@@ -1924,7 +1924,7 @@
       <c r="Y15" s="10"/>
       <c r="Z15" s="10"/>
     </row>
-    <row r="16">
+    <row r="16" ht="112.5" customHeight="1">
       <c r="A16" s="6" t="s">
         <v>98</v>
       </c>
@@ -1970,7 +1970,7 @@
       <c r="Y16" s="10"/>
       <c r="Z16" s="10"/>
     </row>
-    <row r="17">
+    <row r="17" ht="112.5" customHeight="1">
       <c r="A17" s="6" t="s">
         <v>103</v>
       </c>
@@ -2016,7 +2016,7 @@
       <c r="Y17" s="10"/>
       <c r="Z17" s="10"/>
     </row>
-    <row r="18">
+    <row r="18" ht="112.5" customHeight="1">
       <c r="A18" s="6" t="s">
         <v>109</v>
       </c>
@@ -2062,7 +2062,7 @@
       <c r="Y18" s="10"/>
       <c r="Z18" s="10"/>
     </row>
-    <row r="19">
+    <row r="19" ht="112.5" customHeight="1">
       <c r="A19" s="6" t="s">
         <v>115</v>
       </c>
@@ -2108,7 +2108,7 @@
       <c r="Y19" s="10"/>
       <c r="Z19" s="10"/>
     </row>
-    <row r="20">
+    <row r="20" ht="112.5" customHeight="1">
       <c r="A20" s="6" t="s">
         <v>121</v>
       </c>
@@ -2154,7 +2154,7 @@
       <c r="Y20" s="10"/>
       <c r="Z20" s="10"/>
     </row>
-    <row r="21">
+    <row r="21" ht="112.5" customHeight="1">
       <c r="A21" s="6" t="s">
         <v>127</v>
       </c>
@@ -2200,7 +2200,7 @@
       <c r="Y21" s="10"/>
       <c r="Z21" s="10"/>
     </row>
-    <row r="22">
+    <row r="22" ht="112.5" customHeight="1">
       <c r="A22" s="6" t="s">
         <v>134</v>
       </c>
@@ -2246,7 +2246,7 @@
       <c r="Y22" s="10"/>
       <c r="Z22" s="10"/>
     </row>
-    <row r="23">
+    <row r="23" ht="112.5" customHeight="1">
       <c r="A23" s="6" t="s">
         <v>140</v>
       </c>
@@ -2292,7 +2292,7 @@
       <c r="Y23" s="10"/>
       <c r="Z23" s="10"/>
     </row>
-    <row r="24">
+    <row r="24" ht="112.5" customHeight="1">
       <c r="A24" s="6" t="s">
         <v>146</v>
       </c>
@@ -2338,7 +2338,7 @@
       <c r="Y24" s="10"/>
       <c r="Z24" s="10"/>
     </row>
-    <row r="25">
+    <row r="25" ht="112.5" customHeight="1">
       <c r="A25" s="6" t="s">
         <v>152</v>
       </c>
@@ -2384,7 +2384,7 @@
       <c r="Y25" s="10"/>
       <c r="Z25" s="10"/>
     </row>
-    <row r="26">
+    <row r="26" ht="112.5" customHeight="1">
       <c r="A26" s="6" t="s">
         <v>159</v>
       </c>
@@ -2430,7 +2430,7 @@
       <c r="Y26" s="10"/>
       <c r="Z26" s="10"/>
     </row>
-    <row r="27">
+    <row r="27" ht="112.5" customHeight="1">
       <c r="A27" s="6" t="s">
         <v>166</v>
       </c>
@@ -2476,7 +2476,7 @@
       <c r="Y27" s="10"/>
       <c r="Z27" s="10"/>
     </row>
-    <row r="28">
+    <row r="28" ht="112.5" customHeight="1">
       <c r="A28" s="6" t="s">
         <v>172</v>
       </c>
@@ -2522,7 +2522,7 @@
       <c r="Y28" s="10"/>
       <c r="Z28" s="10"/>
     </row>
-    <row r="29">
+    <row r="29" ht="112.5" customHeight="1">
       <c r="A29" s="6" t="s">
         <v>179</v>
       </c>
@@ -2568,7 +2568,7 @@
       <c r="Y29" s="10"/>
       <c r="Z29" s="10"/>
     </row>
-    <row r="30">
+    <row r="30" ht="112.5" customHeight="1">
       <c r="A30" s="6" t="s">
         <v>185</v>
       </c>
@@ -2614,7 +2614,7 @@
       <c r="Y30" s="10"/>
       <c r="Z30" s="10"/>
     </row>
-    <row r="31">
+    <row r="31" ht="112.5" customHeight="1">
       <c r="A31" s="6" t="s">
         <v>191</v>
       </c>
@@ -2660,7 +2660,7 @@
       <c r="Y31" s="10"/>
       <c r="Z31" s="10"/>
     </row>
-    <row r="32">
+    <row r="32" ht="112.5" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>197</v>
       </c>
@@ -2706,7 +2706,7 @@
       <c r="Y32" s="10"/>
       <c r="Z32" s="10"/>
     </row>
-    <row r="33">
+    <row r="33" ht="112.5" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>203</v>
       </c>
@@ -2752,7 +2752,7 @@
       <c r="Y33" s="10"/>
       <c r="Z33" s="10"/>
     </row>
-    <row r="34">
+    <row r="34" ht="112.5" customHeight="1">
       <c r="A34" s="6" t="s">
         <v>209</v>
       </c>
@@ -2798,7 +2798,7 @@
       <c r="Y34" s="10"/>
       <c r="Z34" s="10"/>
     </row>
-    <row r="35">
+    <row r="35" ht="112.5" customHeight="1">
       <c r="A35" s="6" t="s">
         <v>215</v>
       </c>
@@ -2844,7 +2844,7 @@
       <c r="Y35" s="10"/>
       <c r="Z35" s="10"/>
     </row>
-    <row r="36">
+    <row r="36" ht="112.5" customHeight="1">
       <c r="A36" s="6" t="s">
         <v>222</v>
       </c>
@@ -2890,7 +2890,7 @@
       <c r="Y36" s="10"/>
       <c r="Z36" s="10"/>
     </row>
-    <row r="37">
+    <row r="37" ht="112.5" customHeight="1">
       <c r="A37" s="6" t="s">
         <v>229</v>
       </c>
@@ -2936,7 +2936,7 @@
       <c r="Y37" s="10"/>
       <c r="Z37" s="10"/>
     </row>
-    <row r="38">
+    <row r="38" ht="112.5" customHeight="1">
       <c r="A38" s="6" t="s">
         <v>236</v>
       </c>
@@ -2982,7 +2982,7 @@
       <c r="Y38" s="10"/>
       <c r="Z38" s="10"/>
     </row>
-    <row r="39">
+    <row r="39" ht="112.5" customHeight="1">
       <c r="A39" s="6" t="s">
         <v>242</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="Y39" s="10"/>
       <c r="Z39" s="10"/>
     </row>
-    <row r="40">
+    <row r="40" ht="112.5" customHeight="1">
       <c r="A40" s="6" t="s">
         <v>249</v>
       </c>
@@ -3074,7 +3074,7 @@
       <c r="Y40" s="10"/>
       <c r="Z40" s="10"/>
     </row>
-    <row r="41">
+    <row r="41" ht="112.5" customHeight="1">
       <c r="A41" s="6" t="s">
         <v>256</v>
       </c>
@@ -3120,7 +3120,7 @@
       <c r="Y41" s="10"/>
       <c r="Z41" s="10"/>
     </row>
-    <row r="42">
+    <row r="42" ht="112.5" customHeight="1">
       <c r="A42" s="6" t="s">
         <v>263</v>
       </c>
